--- a/artfynd/A 53463-2024 artfynd.xlsx
+++ b/artfynd/A 53463-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2542,134 +2542,6 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>111428629</v>
-      </c>
-      <c r="B17" t="n">
-        <v>96869</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1268</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Uddbräken</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Polystichum aculeatum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ranneberget (12), 375 m NNV Köttsjöns sydände, Dls</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>348584</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6517909</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Mellerud</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Dalskog</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>OD-Mel-0534</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Claes Kannesten</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Claes Kannesten, Anders Niklasson, Maria Karlsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53463-2024 artfynd.xlsx
+++ b/artfynd/A 53463-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97070552</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/251470</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/251471</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/251472</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/251473</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/251474</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97070555</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1554,6 +1594,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97070605</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55096094</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/340918</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1911,6 +1966,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110990855</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2017,6 +2077,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1450356</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2123,6 +2188,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1450357</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2229,6 +2299,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97070556</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2335,6 +2410,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97070606</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2437,6 +2517,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97070558</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2551,6 +2636,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97070572</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2657,6 +2747,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1230166</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2764,8 +2859,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97070560</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>